--- a/ascend_test_suite/v1.2.rc2/model_list.xlsx
+++ b/ascend_test_suite/v1.2.rc2/model_list.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="88">
   <si>
     <t>模型名称</t>
   </si>
@@ -47,7 +47,7 @@
     <t>910B1</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model DeepSeek-R1-AWQ --tokenizer /home/weight/DeepSeek-R1-AWQ/ -tp 8 --port 4321 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --quantization awq --swap-space 40 --tool-call-parser deepseek_v3</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model DeepSeek-R1-AWQ --tokenizer /home/weight/DeepSeek-R1-AWQ/ -tp 8 --port 4321 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --quantization awq --swap-space 40 --gpu-memory-utilization 0.95 --tool-call-parser deepseek_v3</t>
   </si>
   <si>
     <t>长上下文场景可以加上参数--compute-mla-model-as-mha</t>
@@ -74,7 +74,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2</t>
+      <t>docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5</t>
     </r>
     <r>
       <rPr>
@@ -115,7 +115,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2</t>
+      <t>docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5</t>
     </r>
     <r>
       <rPr>
@@ -140,27 +140,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> --model DeepSeek-R1-0528 --tokenizer /home/weight/DeepSeek-R1-0528/ -tp 16 --port 4321 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-addr 192.168.0.156 --master-port 8008 --nnodes 2 --node-rank 0 --swap-space 40 --tool-call-parser deepseek_v3</t>
+      <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model DeepSeek-R1-0528 --tokenizer /home/weight/DeepSeek-R1-0528/ -tp 16 --port 4321 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-addr 192.168.0.156 --master-port 8008 --nnodes 2 --node-rank 0 --swap-space 40 --tool-call-parser deepseek_v3</t>
     </r>
     <r>
       <rPr>
@@ -181,8 +161,13 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" </t>
+      <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model DeepSeek-R1-0528 --tokenizer /home/weight/DeepSeek-R1-0528/ -tp 16 --port 4321 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-addr 192.168.0.156 --master-port 8008 --nnodes 2 --node-rank 1 --swap-space 40 --tool-call-parser deepseek_v3</t>
     </r>
+  </si>
+  <si>
+    <t>DeepSeek-R1-W8A8</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -191,52 +176,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> --model DeepSeek-R1-0528 --tokenizer /home/weight/DeepSeek-R1-0528/ -tp 16 --port 4321 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-addr 192.168.0.156 --master-port 8008 --nnodes 2 --node-rank 1 --swap-space 40 --tool-call-parser deepseek_v3</t>
-    </r>
-  </si>
-  <si>
-    <t>DeepSeek-R1-W8A8</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> --model DeepSeek-R1-W8A8 --tokenizer /home/weight/DeepSeek-R1-Channel-INT8/ -tp 16 --port 8000 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --gpu-memory-utilization 0.97 --max-num-batched-tokens 2048 --master-addr 192.168.0.77 --master-port 8008 --nnodes 2 --node-rank 0 --swap-space 40 --tool-call-parser deepseek_v3 --tokens-per-prediction 2</t>
+      <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model DeepSeek-R1-W8A8 --tokenizer /home/weight/DeepSeek-R1-Channel-INT8/ -tp 16 --port 8000 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --gpu-memory-utilization 0.97 --max-num-batched-tokens 2048 --master-addr 192.168.0.77 --master-port 8008 --nnodes 2 --node-rank 0 --swap-space 40 --tool-call-parser deepseek_v3 --tokens-per-prediction 1</t>
     </r>
     <r>
       <rPr>
@@ -257,8 +197,13 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" </t>
+      <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model DeepSeek-R1-W8A8 --tokenizer /home/weight/DeepSeek-R1-Channel-INT8/ -tp 16 --port 8000 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --gpu-memory-utilization 0.97 --max-num-batched-tokens 2048 --master-addr 192.168.0.77 --master-port 8008 --nnodes 2 --node-rank 1 --swap-space 40 --tool-call-parser deepseek_v3 --tokens-per-prediction 1</t>
     </r>
+  </si>
+  <si>
+    <t>DeepSeek-V3.1-Terminus-Channel-int8</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -267,52 +212,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> --model DeepSeek-R1-W8A8 --tokenizer /home/weight/DeepSeek-R1-Channel-INT8/ -tp 16 --port 8000 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --gpu-memory-utilization 0.97 --max-num-batched-tokens 2048 --master-addr 192.168.0.77 --master-port 8008 --nnodes 2 --node-rank 1 --swap-space 40 --tool-call-parser deepseek_v3 --tokens-per-prediction 2</t>
-    </r>
-  </si>
-  <si>
-    <t>DeepSeek-V3.1-Terminus-Channel-int8</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> --model DeepSeek-V3.1-Terminus-Channel-int8 --tokenizer /home/weight/DeepSeek-V3.1-Terminus-Channel-int8/ -tp 16 --port 8000 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --gpu-memory-utilization 0.97 --max-num-batched-tokens 2048 --master-addr 192.168.0.77 --master-port 8008 --nnodes 2 --node-rank 0 --swap-space 40 --tool-call-parser deepseek_v3 --tokens-per-prediction 2</t>
+      <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model DeepSeek-V3.1-Terminus-Channel-int8 --tokenizer /home/weight/DeepSeek-V3.1-Terminus-Channel-int8/ -tp 16 --port 8000 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --gpu-memory-utilization 0.97 --max-num-batched-tokens 2048 --master-addr 192.168.0.77 --master-port 8008 --nnodes 2 --node-rank 0 --swap-space 40 --tool-call-parser deepseek_v3 --tokens-per-prediction 1</t>
     </r>
     <r>
       <rPr>
@@ -333,196 +233,224 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" </t>
+      <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model DeepSeek-V3.1-Terminus-Channel-int8 --tokenizer /home/weight/DeepSeek-V3.1-Terminus-Channel-int8/ -tp 16 --port 8000 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --gpu-memory-utilization 0.97 --max-num-batched-tokens 2048 --master-addr 192.168.0.77 --master-port 8008 --nnodes 2 --node-rank 1 --swap-space 40 --tool-call-parser deepseek_v3 --tokens-per-prediction 1</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> --model DeepSeek-V3.1-Terminus-Channel-int8 --tokenizer /home/weight/DeepSeek-V3.1-Terminus-Channel-int8/ -tp 16 --port 8000 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --gpu-memory-utilization 0.97 --max-num-batched-tokens 2048 --master-addr 192.168.0.77 --master-port 8008 --nnodes 2 --node-rank 1 --swap-space 40 --tool-call-parser deepseek_v3 --tokens-per-prediction 2</t>
-    </r>
   </si>
   <si>
     <t>DeepSeek-R1-Distill-Qwen-1.5B</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model DeepSeek-R1-Distill-Qwen-1.5B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-1.5B -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model DeepSeek-R1-Distill-Qwen-1.5B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-1.5B -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>DeepSeek-R1-Distill-Qwen-7B</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model DeepSeek-R1-Distill-Qwen-7B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-7B -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model DeepSeek-R1-Distill-Qwen-7B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-7B -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>DeepSeek-R1-Distill-Qwen-14B</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model DeepSeek-R1-Distill-Qwen-14B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-14B -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model DeepSeek-R1-Distill-Qwen-14B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-14B -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>DeepSeek-R1-Distill-Qwen-32B</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model DeepSeek-R1-Distill-Qwen-32B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-32B -tp 2 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model DeepSeek-R1-Distill-Qwen-32B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-32B -tp 2 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>DeepSeek-R1-Distill-Llama-8B</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model DeepSeek-R1-Distill-Llama-8B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-8B -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser llama3_json</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model DeepSeek-R1-Distill-Llama-8B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-8B -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser llama3_json</t>
   </si>
   <si>
     <t>DeepSeek-R1-Distill-Llama-70B</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model DeepSeek-R1-Distill-Llama-70B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-70B -tp 4 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser llama3_json</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model DeepSeek-R1-Distill-Llama-70B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-70B -tp 4 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser llama3_json</t>
   </si>
   <si>
     <t>Meta-Llama-3.1-8B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Meta-Llama-3.1-8B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-8B-Instruct -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser llama3_json</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Meta-Llama-3.1-8B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-8B-Instruct -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser llama3_json</t>
   </si>
   <si>
     <t>Meta-Llama-3.1-70B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Meta-Llama-3.1-70B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-70B-Instruct -tp 4 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser llama3_json</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Meta-Llama-3.1-70B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-70B-Instruct -tp 4 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser llama3_json</t>
   </si>
   <si>
     <t>Qwen2.5-0.5B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Qwen2.5-0.5B-Instruct --tokenizer /home/weight/Qwen2.5-0.5B-Instruct -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen2.5-0.5B-Instruct --tokenizer /home/weight/Qwen2.5-0.5B-Instruct -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-1.5B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Qwen2.5-1.5B-Instruct --tokenizer /home/weight/Qwen2.5-1.5B-Instruct -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen2.5-1.5B-Instruct --tokenizer /home/weight/Qwen2.5-1.5B-Instruct -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-3B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Qwen2.5-3B-Instruct --tokenizer /home/weight/Qwen2.5-3B-Instruct -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen2.5-3B-Instruct --tokenizer /home/weight/Qwen2.5-3B-Instruct -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-7B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Qwen2.5-7B-Instruct --tokenizer /home/weight/Qwen2.5-7B-Instruct -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen2.5-7B-Instruct --tokenizer /home/weight/Qwen2.5-7B-Instruct -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-14B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Qwen2.5-14B-Instruct --tokenizer /home/weight/Qwen2.5-14B-Instruct -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen2.5-14B-Instruct --tokenizer /home/weight/Qwen2.5-14B-Instruct -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-32B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Qwen2.5-32B-Instruct --tokenizer /home/weight/Qwen2.5-32B-Instruct -tp 2 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen2.5-32B-Instruct --tokenizer /home/weight/Qwen2.5-32B-Instruct -tp 2 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-72B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Qwen2.5-72B-Instruct --tokenizer /home/weight/Qwen2.5-72B-Instruct -tp 4 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen2.5-72B-Instruct --tokenizer /home/weight/Qwen2.5-72B-Instruct -tp 4 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>QwQ-32B</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model QwQ-32B --tokenizer /home/weight/QwQ-32B -tp 2 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model QwQ-32B --tokenizer /home/weight/QwQ-32B -tp 2 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-0.5B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Qwen2.5-0.5B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-0.5B-Instruct-AWQ -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen2.5-0.5B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-0.5B-Instruct-AWQ -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-1.5B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Qwen2.5-1.5B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-1.5B-Instruct-AWQ -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen2.5-1.5B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-1.5B-Instruct-AWQ -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-3B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Qwen2.5-3B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-3B-Instruct-AWQ -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen2.5-3B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-3B-Instruct-AWQ -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-7B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Qwen2.5-7B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-7B-Instruct-AWQ -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen2.5-7B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-7B-Instruct-AWQ -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-14B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Qwen2.5-14B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-14B-Instruct-AWQ -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen2.5-14B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-14B-Instruct-AWQ -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-32B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Qwen2.5-32B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-32B-Instruct-AWQ -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen2.5-32B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-32B-Instruct-AWQ -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-72B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Qwen2.5-72B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-72B-Instruct-AWQ -tp 2 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen2.5-72B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-72B-Instruct-AWQ -tp 2 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>QwQ-32B-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model QwQ-32B-AWQ --tokenizer /home/weight/QwQ-32B-AWQ -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model QwQ-32B-AWQ --tokenizer /home/weight/QwQ-32B-AWQ -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen3-32B</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Qwen3-32B --tokenizer /home/weight/Qwen3/Qwen3-32B -tp 2 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen3-32B --tokenizer /home/weight/Qwen3/Qwen3-32B -tp 2 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen3-30B-A3B</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Qwen3-30B-A3B --tokenizer /home/weight/Qwen3/Qwen3-30B-A3B -tp 2 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen3-30B-A3B --tokenizer /home/weight/Qwen3/Qwen3-30B-A3B -tp 2 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen3-235B-A22B</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Qwen3-235B-A22B --tokenizer /home/weight/Qwen3/Qwen3-235B-A22B -tp 8 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen3-235B-A22B --tokenizer /home/weight/Qwen3/Qwen3-235B-A22B -tp 8 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen3-32B-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Qwen3-32B-AWQ --tokenizer /home/weight/Qwen3/Qwen3-32B-AWQ -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen3-32B-AWQ --tokenizer /home/weight/Qwen3/Qwen3-32B-AWQ -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes</t>
+  </si>
+  <si>
+    <t>Qwen1.5-1.8B-Chat</t>
+  </si>
+  <si>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen1.5-1.8B-Chat --tokenizer /home/weight/Qwen1.5-1.8B-Chat -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40</t>
+  </si>
+  <si>
+    <t>ChatGLM-6B</t>
+  </si>
+  <si>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model ChatGLM-6B --tokenizer /home/weight/ChatGLM-6B -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40</t>
+  </si>
+  <si>
+    <t>chatglm2-6b</t>
+  </si>
+  <si>
+    <t>910B2</t>
+  </si>
+  <si>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model chatglm2-6b --tokenizer /home/weight/chatglm2-6b -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40</t>
+  </si>
+  <si>
+    <t>chatglm3-6b</t>
+  </si>
+  <si>
+    <t>910B3</t>
+  </si>
+  <si>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model chatglm3-6b --tokenizer /home/weight/chatglm3-6b -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40</t>
+  </si>
+  <si>
+    <t>baichuan-7B</t>
+  </si>
+  <si>
+    <t>910B4</t>
+  </si>
+  <si>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model baichuan-7B --tokenizer /home/weight/baichuan-7B -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40</t>
+  </si>
+  <si>
+    <t>Baichuan2-7B-Chat</t>
+  </si>
+  <si>
+    <t>910B5</t>
+  </si>
+  <si>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Baichuan2-7B-Chat --tokenizer /home/weight/Baichuan2-7B-Chat -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40</t>
   </si>
 </sst>
 </file>
@@ -535,7 +463,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -553,6 +481,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1037,137 +972,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1175,6 +1110,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1702,10 +1640,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T34"/>
+  <dimension ref="A1:T40"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="39.9090909090909" customWidth="1"/>
+    <col min="2" max="2" width="6.54545454545455" customWidth="1"/>
+    <col min="3" max="3" width="255.636363636364" customWidth="1"/>
+    <col min="4" max="4" width="51.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -2668,14 +2609,177 @@
       <c r="S34" s="2"/>
       <c r="T34" s="2"/>
     </row>
+    <row r="35" spans="1:20">
+      <c r="A35" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="2"/>
+    </row>
+    <row r="36" spans="1:20">
+      <c r="A36" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+    </row>
+    <row r="37" spans="1:20">
+      <c r="A37" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
+      <c r="T37" s="2"/>
+    </row>
+    <row r="38" spans="1:20">
+      <c r="A38" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
+      <c r="T38" s="2"/>
+    </row>
+    <row r="39" spans="1:20">
+      <c r="A39" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="2"/>
+      <c r="T39" s="2"/>
+    </row>
+    <row r="40" spans="1:20">
+      <c r="A40" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="2"/>
+      <c r="T40" s="2"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model DeepSeek-R1-AWQ --tokenizer /home/weight/DeepSeek-R1-AWQ/ -tp 8 --port 4321 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --quantization awq --swap-space 40 --tool-call-parser deepseek_" tooltip="http://docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2"/>
-    <hyperlink ref="C11" r:id="rId1" display="docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model DeepSeek-R1-Distill-Llama-8B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-8B -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser lla" tooltip="http://docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2"/>
-    <hyperlink ref="C12" r:id="rId1" display="docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model DeepSeek-R1-Distill-Llama-70B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-70B -tp 4 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser l" tooltip="http://docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2"/>
-    <hyperlink ref="C13" r:id="rId1" display="docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Meta-Llama-3.1-8B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-8B-Instruct -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser llama3_" tooltip="http://docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2"/>
-    <hyperlink ref="C14" r:id="rId1" display="docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Meta-Llama-3.1-70B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-70B-Instruct -tp 4 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser llama" tooltip="http://docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2"/>
-    <hyperlink ref="C33" r:id="rId1" display="docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2 --model Qwen3-235B-A22B --tokenizer /home/weight/Qwen3/Qwen3-235B-A22B -tp 8 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --platform-type ascend --swap-space 40 --tool-call-" tooltip="http://docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc2"/>
+    <hyperlink ref="C2" r:id="rId1" display="docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model DeepSeek-R1-AWQ --tokenizer /home/weight/DeepSeek-R1-AWQ/ -tp 8 --port 4321 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --quantization awq --swap-space 40 --gpu-memory-utilization 0.9" tooltip="http://docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
